--- a/data/trans_camb/IP28_R-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-0.63594336382434</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.120892813193607</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.9352043346467096</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.47643934330944</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.772302707094875</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.07024279609272113</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-2.8676026342848</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.805006784503179</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.36612886773375</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.552543543801157</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-2.36120028738915</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.098160159054445</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>1.384194002271452</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.152547445197818</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7801450342508071</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.8959550313522715</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.8878056050174929</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2.970593192261644</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.2409295629409043</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.4246545069081515</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.4182476051012458</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.6603019217716819</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.3165503995080653</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.02879102321077698</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.7298080503752817</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.6011548878242222</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.8901340041068594</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6921887785437207</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7045521703839053</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>1.027711384443836</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3.65535877310196</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.8267379071940224</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>5.528747015280186</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.5923377290993275</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.69869280834302</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-0.5940581690780721</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.6811542973982598</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.296334283090322</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.5659358392023642</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.422102032010365</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.6515779878040119</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-1.957772593077586</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.319749515771662</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.465176872611413</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.019790006487495</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-2.831072154088059</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-2.195257430572496</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>0.6124013620434533</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.2910834779284954</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-0.432540202506065</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.139054621992996</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-0.4024722023328152</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.7434070726066133</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.6033966696098556</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.6918619353023929</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.866385394385877</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.2135222858688457</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.7924212824876135</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3630711813317981</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -807,13 +866,18 @@
       </c>
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.7809046296166645</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.8223106356779136</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -824,13 +888,18 @@
       </c>
       <c r="C15" s="6" t="inlineStr"/>
       <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="n">
+        <v>-0.02529469121610582</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2.012750219402481</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.04241367731874257</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.9513463076630763</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +912,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-0.9191999829343619</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.3683239232959006</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.4332662510797114</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.01509106539982416</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.2427658034690886</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.1805532787392916</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +938,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-3.030522426479437</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.435125518643036</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.074932736000771</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.07302167243966</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-1.24648763190268</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-1.210220462151974</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +964,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.8185539343428203</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.377816666733381</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.731727370359709</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.9127173891794547</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.8506846934657675</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +990,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.4007005332181363</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.8188968521851616</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.02852293692675087</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.333285875466286</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.2478761700084146</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -917,9 +1022,6 @@
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -934,9 +1036,6 @@
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr"/>
       <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1048,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.7890100857583741</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-1.067094123996844</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.1738369848091496</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.9466973382256771</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.5049352763095819</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.9919979059995473</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1074,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-4.121667828935019</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-4.876864449708655</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-5.141227734054669</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-5.158309342220764</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-2.807988868197561</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-3.346675124482904</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1100,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>1.723653117207883</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.9019189546579671</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2.894223922434219</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.151731764791419</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.634610031429555</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.6436027278895922</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1126,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.4806092425723605</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.6499984067942528</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.08530750588248379</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.4645754114884303</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.2772943879223194</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.5447736869858046</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1022,10 +1157,9 @@
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1039,10 +1173,9 @@
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="n">
+        <v>1.583090548101014</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1188,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.6103986810367316</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-0.6771750341855214</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.9336914846229902</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-0.7705850654573467</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.7674440891504433</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-0.7266873821110409</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1214,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-1.72784620643216</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-1.775646468074978</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-2.044585790260093</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-1.917595722797064</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-1.564792624361242</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-1.524030226037145</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1240,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.280351850803259</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.2893306465433478</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.1222369036525294</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.6064885409250683</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.07099850687207744</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.02768313573974233</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1266,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.3774528804295756</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.4187454448200885</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.4780162431181126</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.3945116604994856</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.4310457733913636</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.4081541952880882</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1292,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.7471220993139301</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.7849240989365961</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.7607333862070768</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.7379462942961514</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.6952095673079212</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.686339325698325</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1318,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.3036574589951634</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.3238551761178528</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.1965493236971619</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.5169206255942755</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.0338250061412512</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.02997511129358368</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1346,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
